--- a/events/Krakow_2015_WC/Krakow_2015_WC_start.xlsx
+++ b/events/Krakow_2015_WC/Krakow_2015_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W674"/>
+  <dimension ref="A1:AC674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1494,7 @@
           <t>PUTNINS Emils</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>63159</t>
         </is>
@@ -1522,7 +1552,7 @@
           <t>BONDAR Oleksandr</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>61371</t>
         </is>
@@ -1580,7 +1610,7 @@
           <t>LUKASS Andars</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>44865</t>
         </is>
@@ -1638,7 +1668,7 @@
           <t>WANG Sheng</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>60989</t>
         </is>
@@ -1696,7 +1726,7 @@
           <t>YILMAZ Emre</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>60067</t>
         </is>
@@ -1754,7 +1784,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -1812,7 +1842,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -1870,7 +1900,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -1928,7 +1958,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -1986,7 +2016,7 @@
           <t>DEMIRCI Ismail</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>39914</t>
         </is>
@@ -2044,7 +2074,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -2102,7 +2132,7 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -2160,7 +2190,7 @@
           <t>BLAISE Thibault</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>41589</t>
         </is>
@@ -2218,7 +2248,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -2276,7 +2306,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -2334,7 +2364,7 @@
           <t>HODSON Ethan</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
@@ -2392,7 +2422,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -2503,7 +2533,7 @@
           <t>DOMENJO Jordi</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>35739</t>
         </is>
@@ -2561,7 +2591,7 @@
           <t>FOULON Kilian</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35602</t>
         </is>
@@ -2619,7 +2649,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -2677,7 +2707,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -2735,7 +2765,7 @@
           <t>HETSMAN Anton</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>41691</t>
         </is>
@@ -2793,7 +2823,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -2851,7 +2881,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -2962,7 +2992,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -3020,7 +3050,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -3078,7 +3108,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -3136,7 +3166,7 @@
           <t>GARMENDIA Aitor</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>35745</t>
         </is>
@@ -3194,7 +3224,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -3305,7 +3335,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -3363,7 +3393,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -3421,7 +3451,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -3479,7 +3509,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -3537,7 +3567,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -3595,7 +3625,7 @@
           <t>PFEIFFER Frederick</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>39878</t>
         </is>
@@ -3653,7 +3683,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -3711,7 +3741,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -3769,7 +3799,7 @@
           <t>JEFFERY Robin</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>36525</t>
         </is>
@@ -3827,7 +3857,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -3885,7 +3915,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -3943,7 +3973,7 @@
           <t>LIPATOV Aleksandr</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
@@ -4001,7 +4031,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -4059,7 +4089,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -4117,7 +4147,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -4175,7 +4205,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -4286,7 +4316,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -4344,7 +4374,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -4402,7 +4432,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -4460,7 +4490,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -4518,7 +4548,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -4576,7 +4606,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -4634,7 +4664,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -4692,7 +4722,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -4750,7 +4780,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -4808,7 +4838,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -4866,7 +4896,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -4924,7 +4954,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -4982,7 +5012,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -5040,7 +5070,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -5098,7 +5128,7 @@
           <t>DUANGLAHWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -5156,7 +5186,7 @@
           <t>MURZINA Juta</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>39930</t>
         </is>
@@ -5267,7 +5297,7 @@
           <t>KRAUJA Santa</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>42927</t>
         </is>
@@ -5325,7 +5355,7 @@
           <t>HURKALA Ewa</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>43976</t>
         </is>
@@ -5489,7 +5519,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -5600,7 +5630,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -5658,7 +5688,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -5716,7 +5746,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -5774,7 +5804,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -5832,7 +5862,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -5890,7 +5920,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -5948,7 +5978,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -6006,7 +6036,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -6064,7 +6094,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -6122,7 +6152,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -6180,7 +6210,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -6238,7 +6268,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -6349,7 +6379,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -6407,7 +6437,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -6465,7 +6495,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -6523,7 +6553,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -6581,7 +6611,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -6745,7 +6775,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -6803,7 +6833,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -6914,7 +6944,7 @@
           <t>TARKKA Teijo</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>35804</t>
         </is>
@@ -6972,7 +7002,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -7030,7 +7060,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -7088,7 +7118,7 @@
           <t>PAKERS Kaspars</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>42940</t>
         </is>
@@ -7146,7 +7176,7 @@
           <t>PESTOV Ruslan</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>36138</t>
         </is>
@@ -7204,7 +7234,7 @@
           <t>OGURA Takashi</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>37679</t>
         </is>
@@ -7262,7 +7292,7 @@
           <t>NIKOLOVSKI Atanas</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>35582</t>
         </is>
@@ -7320,7 +7350,7 @@
           <t>JANCEK Lubomir</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>35362</t>
         </is>
@@ -7378,7 +7408,7 @@
           <t>ACAR Anil</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>39900</t>
         </is>
@@ -7436,7 +7466,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -7494,7 +7524,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -7552,7 +7582,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -7610,7 +7640,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -7668,7 +7698,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -7726,7 +7756,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -7784,7 +7814,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -7842,7 +7872,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -7900,7 +7930,7 @@
           <t>TAN Ya</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
@@ -7958,7 +7988,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -8016,7 +8046,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -8074,7 +8104,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -8132,7 +8162,7 @@
           <t>URANO Shuhei</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>44317</t>
         </is>
@@ -8190,7 +8220,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -8248,7 +8278,7 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -8306,7 +8336,7 @@
           <t>DAMIENS Bastien</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35584</t>
         </is>
@@ -8364,7 +8394,7 @@
           <t>CVIKL Ondrej</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>35946</t>
         </is>
@@ -8422,7 +8452,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -8480,7 +8510,7 @@
           <t>DAVIDSON Elliott</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
@@ -8538,7 +8568,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -8596,7 +8626,7 @@
           <t>PAN Hung-Ming</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>37001</t>
         </is>
@@ -8654,7 +8684,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -8712,7 +8742,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -8770,7 +8800,7 @@
           <t>ROUICH Mehdi</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>36944</t>
         </is>
@@ -8828,7 +8858,7 @@
           <t>DANGEN Jack</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>51865</t>
         </is>
@@ -8886,7 +8916,7 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -8997,7 +9027,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -9055,7 +9085,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -9113,7 +9143,7 @@
           <t>SEKER Enzo</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>39917</t>
         </is>
@@ -9171,7 +9201,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -9229,7 +9259,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -9287,7 +9317,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -9345,7 +9375,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -9403,7 +9433,7 @@
           <t>KARAMARKO Filip</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>35596</t>
         </is>
@@ -9461,7 +9491,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -9519,7 +9549,7 @@
           <t>MRKOCI Marko</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>35592</t>
         </is>
@@ -9577,7 +9607,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -9635,7 +9665,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -9746,7 +9776,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -9804,7 +9834,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -9862,7 +9892,7 @@
           <t>LANGER Andreas</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>35295</t>
         </is>
@@ -9920,7 +9950,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -9978,7 +10008,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -10089,7 +10119,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -10147,7 +10177,7 @@
           <t>OBLINGER Helmut</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>35281</t>
         </is>
@@ -10205,7 +10235,7 @@
           <t>SAJBIDOR Jan</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>35236</t>
         </is>
@@ -10263,7 +10293,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -10321,7 +10351,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -10379,7 +10409,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -10490,7 +10520,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -10548,7 +10578,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -10606,7 +10636,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -10664,7 +10694,7 @@
           <t>MOLMENTI Daniele</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
@@ -10722,7 +10752,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -10780,7 +10810,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -10838,7 +10868,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -10896,7 +10926,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -10954,7 +10984,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -11012,7 +11042,7 @@
           <t>ROMEO Andrea</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>35502</t>
         </is>
@@ -11070,7 +11100,7 @@
           <t>KURT Michael</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
@@ -11128,7 +11158,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -11186,7 +11216,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -11244,7 +11274,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -11302,7 +11332,7 @@
           <t>BOECKELMANN Paul</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>35118</t>
         </is>
@@ -11360,7 +11390,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -11418,7 +11448,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -11476,7 +11506,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -11534,7 +11564,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -11592,7 +11622,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -11650,7 +11680,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -11708,7 +11738,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -11766,7 +11796,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -11824,7 +11854,7 @@
           <t>PUTNINS Emils</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>63159</t>
         </is>
@@ -11882,7 +11912,7 @@
           <t>BONDAR Oleksandr</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>61371</t>
         </is>
@@ -11940,7 +11970,7 @@
           <t>LUKASS Andars</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>44865</t>
         </is>
@@ -11998,7 +12028,7 @@
           <t>WANG Sheng</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>60989</t>
         </is>
@@ -12056,7 +12086,7 @@
           <t>YILMAZ Emre</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>60067</t>
         </is>
@@ -12114,7 +12144,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -12172,7 +12202,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -12230,7 +12260,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -12288,7 +12318,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -12346,7 +12376,7 @@
           <t>DEMIRCI Ismail</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>39914</t>
         </is>
@@ -12404,7 +12434,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -12462,7 +12492,7 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -12520,7 +12550,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -12578,7 +12608,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -12636,7 +12666,7 @@
           <t>HODSON Ethan</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
@@ -12694,7 +12724,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -12805,7 +12835,7 @@
           <t>FOULON Kilian</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>35602</t>
         </is>
@@ -12863,7 +12893,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -12921,7 +12951,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -12979,7 +13009,7 @@
           <t>HETSMAN Anton</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>41691</t>
         </is>
@@ -13037,7 +13067,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -13095,7 +13125,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -13153,7 +13183,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -13211,7 +13241,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -13269,7 +13299,7 @@
           <t>GARMENDIA Aitor</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>35745</t>
         </is>
@@ -13327,7 +13357,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -13438,7 +13468,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -13496,7 +13526,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -13554,7 +13584,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -13612,7 +13642,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -13670,7 +13700,7 @@
           <t>PFEIFFER Frederick</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>39878</t>
         </is>
@@ -13728,7 +13758,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -13786,7 +13816,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -13844,7 +13874,7 @@
           <t>LIPATOV Aleksandr</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
@@ -13902,7 +13932,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -13960,7 +13990,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -14018,7 +14048,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -14076,7 +14106,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -14134,7 +14164,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -14192,7 +14222,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -14250,7 +14280,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -14308,7 +14338,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -14366,7 +14396,7 @@
           <t>DUANGLAHWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -14424,7 +14454,7 @@
           <t>MURZINA Juta</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>39930</t>
         </is>
@@ -14535,7 +14565,7 @@
           <t>KRAUJA Santa</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>42927</t>
         </is>
@@ -14593,7 +14623,7 @@
           <t>HURKALA Ewa</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>43976</t>
         </is>
@@ -14704,7 +14734,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -14815,7 +14845,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -14873,7 +14903,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -14931,7 +14961,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -14989,7 +15019,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -15047,7 +15077,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -15105,7 +15135,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -15163,7 +15193,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -15274,7 +15304,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -15332,7 +15362,7 @@
           <t>TARKKA Teijo</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>35804</t>
         </is>
@@ -15390,7 +15420,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -15448,7 +15478,7 @@
           <t>PAKERS Kaspars</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>42940</t>
         </is>
@@ -15506,7 +15536,7 @@
           <t>PESTOV Ruslan</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>36138</t>
         </is>
@@ -15564,7 +15594,7 @@
           <t>OGURA Takashi</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>37679</t>
         </is>
@@ -15622,7 +15652,7 @@
           <t>NIKOLOVSKI Atanas</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>35582</t>
         </is>
@@ -15680,7 +15710,7 @@
           <t>JANCEK Lubomir</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>35362</t>
         </is>
@@ -15738,7 +15768,7 @@
           <t>ACAR Anil</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>39900</t>
         </is>
@@ -15796,7 +15826,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -15854,7 +15884,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -15912,7 +15942,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -15970,7 +16000,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -16028,7 +16058,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -16086,7 +16116,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -16144,7 +16174,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -16202,7 +16232,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -16260,7 +16290,7 @@
           <t>TAN Ya</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
@@ -16318,7 +16348,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -16376,7 +16406,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -16434,7 +16464,7 @@
           <t>URANO Shuhei</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>44317</t>
         </is>
@@ -16492,7 +16522,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -16550,7 +16580,7 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -16608,7 +16638,7 @@
           <t>CVIKL Ondrej</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>35946</t>
         </is>
@@ -16666,7 +16696,7 @@
           <t>DAVIDSON Elliott</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
@@ -16724,7 +16754,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -16782,7 +16812,7 @@
           <t>PAN Hung-Ming</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>37001</t>
         </is>
@@ -16840,7 +16870,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -16898,7 +16928,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -16956,7 +16986,7 @@
           <t>ROUICH Mehdi</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>36944</t>
         </is>
@@ -17014,7 +17044,7 @@
           <t>DANGEN Jack</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>51865</t>
         </is>
@@ -17072,7 +17102,7 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -17183,7 +17213,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -17241,7 +17271,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -17299,7 +17329,7 @@
           <t>SEKER Enzo</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>39917</t>
         </is>
@@ -17357,7 +17387,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -17415,7 +17445,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -17473,7 +17503,7 @@
           <t>KARAMARKO Filip</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>35596</t>
         </is>
@@ -17531,7 +17561,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -17589,7 +17619,7 @@
           <t>MRKOCI Marko</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>35592</t>
         </is>
@@ -17647,7 +17677,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -17705,7 +17735,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -17816,7 +17846,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -17874,7 +17904,7 @@
           <t>LANGER Andreas</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>35295</t>
         </is>
@@ -17932,7 +17962,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -18043,7 +18073,7 @@
           <t>OBLINGER Helmut</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>35281</t>
         </is>
@@ -18101,7 +18131,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -18212,7 +18242,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -18270,7 +18300,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -18328,7 +18358,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -18386,7 +18416,7 @@
           <t>BOECKELMANN Paul</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>35118</t>
         </is>
@@ -18444,7 +18474,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -18502,7 +18532,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -18560,7 +18590,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -18618,7 +18648,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -18676,7 +18706,7 @@
           <t>FAGERLUND Amanda</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>43406</t>
         </is>
@@ -18734,7 +18764,7 @@
           <t>OKAZAKI Haruka</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>42265</t>
         </is>
@@ -18792,7 +18822,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -18850,7 +18880,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -18908,7 +18938,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -18966,7 +18996,7 @@
           <t>CWIK Sara</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>43978</t>
         </is>
@@ -19024,7 +19054,7 @@
           <t>OROKOCKA Viktoria</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>35667</t>
         </is>
@@ -19082,7 +19112,7 @@
           <t>NEIME Julie</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>35679</t>
         </is>
@@ -19140,7 +19170,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -19198,7 +19228,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -19256,7 +19286,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -19314,7 +19344,7 @@
           <t>HASSOVA Michaela</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>41783</t>
         </is>
@@ -19425,7 +19455,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -19483,7 +19513,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -19541,7 +19571,7 @@
           <t>DANGEN Haylee</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>42108</t>
         </is>
@@ -19599,7 +19629,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -19657,7 +19687,7 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -19715,7 +19745,7 @@
           <t>FROEHLICH Thea</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
@@ -19773,7 +19803,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -19831,7 +19861,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -19889,7 +19919,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -19947,7 +19977,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -20005,7 +20035,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -20063,7 +20093,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -20121,7 +20151,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -20179,7 +20209,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -20237,7 +20267,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -20348,7 +20378,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -20406,7 +20436,7 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -20464,7 +20494,7 @@
           <t>ORNSTOVA Eva</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>35052</t>
         </is>
@@ -20522,7 +20552,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -20633,7 +20663,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -20691,7 +20721,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -20749,7 +20779,7 @@
           <t>LI Lu</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>37086</t>
         </is>
@@ -20807,7 +20837,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -20918,7 +20948,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -20976,7 +21006,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -21034,7 +21064,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -21092,7 +21122,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -21150,7 +21180,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -21208,7 +21238,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -21266,7 +21296,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -21324,7 +21354,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -21382,7 +21412,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -21440,7 +21470,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -21551,7 +21581,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -21609,7 +21639,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -21667,7 +21697,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -21725,7 +21755,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -21783,7 +21813,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -21841,7 +21871,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -21952,7 +21982,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -22015,12 +22045,12 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
       </c>
-      <c r="V377" t="inlineStr">
+      <c r="Y377" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -22083,12 +22113,12 @@
           <t>BONDAR Oleksandr</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>42877</t>
         </is>
       </c>
-      <c r="V378" t="inlineStr">
+      <c r="Y378" t="inlineStr">
         <is>
           <t>61371</t>
         </is>
@@ -22151,12 +22181,12 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
       </c>
-      <c r="V379" t="inlineStr">
+      <c r="Y379" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -22219,12 +22249,12 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
       </c>
-      <c r="V380" t="inlineStr">
+      <c r="Y380" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -22287,7 +22317,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="V381" t="inlineStr">
+      <c r="Y381" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -22350,12 +22380,12 @@
           <t>SUSLOV Alexei</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
       </c>
-      <c r="V382" t="inlineStr">
+      <c r="Y382" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
@@ -22418,7 +22448,7 @@
           <t>FRANKLIN Zachary</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -22481,12 +22511,12 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
       </c>
-      <c r="V384" t="inlineStr">
+      <c r="Y384" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -22549,12 +22579,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V385" t="inlineStr">
+      <c r="Y385" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -22617,12 +22647,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V386" t="inlineStr">
+      <c r="Y386" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -22685,12 +22715,12 @@
           <t>SKAKALA Juraj</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
       </c>
-      <c r="V387" t="inlineStr">
+      <c r="Y387" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
@@ -22753,12 +22783,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V388" t="inlineStr">
+      <c r="Y388" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -22821,12 +22851,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V389" t="inlineStr">
+      <c r="Y389" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -22889,12 +22919,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V390" t="inlineStr">
+      <c r="Y390" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -22957,12 +22987,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V391" t="inlineStr">
+      <c r="Y391" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -23025,12 +23055,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V392" t="inlineStr">
+      <c r="Y392" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -23093,12 +23123,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V393" t="inlineStr">
+      <c r="Y393" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -23161,12 +23191,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V394" t="inlineStr">
+      <c r="Y394" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -23229,12 +23259,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V395" t="inlineStr">
+      <c r="Y395" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -23297,12 +23327,12 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
       </c>
-      <c r="V396" t="inlineStr">
+      <c r="Y396" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -23365,12 +23395,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V397" t="inlineStr">
+      <c r="Y397" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -23491,12 +23521,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V399" t="inlineStr">
+      <c r="Y399" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -23559,12 +23589,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V400" t="inlineStr">
+      <c r="Y400" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -23627,12 +23657,12 @@
           <t>LARIONOV Dmitry</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>35449</t>
         </is>
       </c>
-      <c r="V401" t="inlineStr">
+      <c r="Y401" t="inlineStr">
         <is>
           <t>35450</t>
         </is>
@@ -23695,12 +23725,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V402" t="inlineStr">
+      <c r="Y402" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -23763,12 +23793,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V403" t="inlineStr">
+      <c r="Y403" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -23831,12 +23861,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V404" t="inlineStr">
+      <c r="Y404" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -23899,12 +23929,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V405" t="inlineStr">
+      <c r="Y405" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -23967,12 +23997,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V406" t="inlineStr">
+      <c r="Y406" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -24035,12 +24065,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V407" t="inlineStr">
+      <c r="Y407" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -24103,12 +24133,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V408" t="inlineStr">
+      <c r="Y408" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -24171,12 +24201,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V409" t="inlineStr">
+      <c r="Y409" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -24239,7 +24269,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -24302,12 +24332,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V411" t="inlineStr">
+      <c r="Y411" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -24370,12 +24400,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V412" t="inlineStr">
+      <c r="Y412" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -24433,7 +24463,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -24491,7 +24521,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -24549,7 +24579,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -24607,7 +24637,7 @@
           <t>FAGERLUND Amanda</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>43406</t>
         </is>
@@ -24665,7 +24695,7 @@
           <t>OKAZAKI Haruka</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>42265</t>
         </is>
@@ -24723,7 +24753,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -24781,7 +24811,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -24839,7 +24869,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -24897,7 +24927,7 @@
           <t>CWIK Sara</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>43978</t>
         </is>
@@ -24955,7 +24985,7 @@
           <t>OROKOCKA Viktoria</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>35667</t>
         </is>
@@ -25013,7 +25043,7 @@
           <t>NEIME Julie</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>35679</t>
         </is>
@@ -25071,7 +25101,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -25129,7 +25159,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -25187,7 +25217,7 @@
           <t>HASSOVA Michaela</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>41783</t>
         </is>
@@ -25298,7 +25328,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -25356,7 +25386,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -25414,7 +25444,7 @@
           <t>DANGEN Haylee</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>42108</t>
         </is>
@@ -25472,7 +25502,7 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -25530,7 +25560,7 @@
           <t>FROEHLICH Thea</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
@@ -25588,7 +25618,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -25646,7 +25676,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -25704,7 +25734,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -25762,7 +25792,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -25820,7 +25850,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -25878,7 +25908,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -25936,7 +25966,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -25994,7 +26024,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -26052,7 +26082,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -26163,7 +26193,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -26221,7 +26251,7 @@
           <t>LI Lu</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>37086</t>
         </is>
@@ -26332,7 +26362,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -26390,7 +26420,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -26448,7 +26478,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -26506,7 +26536,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -26564,7 +26594,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -26622,7 +26652,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -26680,7 +26710,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -26738,7 +26768,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -26796,7 +26826,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -26859,12 +26889,12 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
       </c>
-      <c r="V455" t="inlineStr">
+      <c r="Y455" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -26927,12 +26957,12 @@
           <t>BONDAR Oleksandr</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>42877</t>
         </is>
       </c>
-      <c r="V456" t="inlineStr">
+      <c r="Y456" t="inlineStr">
         <is>
           <t>61371</t>
         </is>
@@ -26995,12 +27025,12 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
       </c>
-      <c r="V457" t="inlineStr">
+      <c r="Y457" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -27063,12 +27093,12 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
       </c>
-      <c r="V458" t="inlineStr">
+      <c r="Y458" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -27131,7 +27161,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="V459" t="inlineStr">
+      <c r="Y459" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -27194,12 +27224,12 @@
           <t>SUSLOV Alexei</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
       </c>
-      <c r="V460" t="inlineStr">
+      <c r="Y460" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
@@ -27262,12 +27292,12 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
       </c>
-      <c r="V461" t="inlineStr">
+      <c r="Y461" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -27330,12 +27360,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V462" t="inlineStr">
+      <c r="Y462" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -27398,12 +27428,12 @@
           <t>SKAKALA Juraj</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
       </c>
-      <c r="V463" t="inlineStr">
+      <c r="Y463" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
@@ -27466,12 +27496,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V464" t="inlineStr">
+      <c r="Y464" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -27534,12 +27564,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V465" t="inlineStr">
+      <c r="Y465" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -27602,12 +27632,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V466" t="inlineStr">
+      <c r="Y466" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -27670,12 +27700,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V467" t="inlineStr">
+      <c r="Y467" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -27738,12 +27768,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V468" t="inlineStr">
+      <c r="Y468" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -27806,12 +27836,12 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
       </c>
-      <c r="V469" t="inlineStr">
+      <c r="Y469" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -27874,12 +27904,12 @@
           <t>LARIONOV Dmitry</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>35449</t>
         </is>
       </c>
-      <c r="V470" t="inlineStr">
+      <c r="Y470" t="inlineStr">
         <is>
           <t>35450</t>
         </is>
@@ -27942,12 +27972,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V471" t="inlineStr">
+      <c r="Y471" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -28010,12 +28040,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V472" t="inlineStr">
+      <c r="Y472" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -28078,12 +28108,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V473" t="inlineStr">
+      <c r="Y473" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -28146,12 +28176,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V474" t="inlineStr">
+      <c r="Y474" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -28214,7 +28244,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -28585,7 +28615,7 @@
           <t>WANG Sheng</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>60989</t>
         </is>
@@ -28643,7 +28673,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -28701,7 +28731,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -28759,7 +28789,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -28817,7 +28847,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -28875,7 +28905,7 @@
           <t>HODSON Ethan</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
@@ -28933,7 +28963,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -28991,7 +29021,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -29049,7 +29079,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -29107,7 +29137,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -29165,7 +29195,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -29223,7 +29253,7 @@
           <t>JEFFERY Robin</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>36525</t>
         </is>
@@ -29281,7 +29311,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -29339,7 +29369,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -29397,7 +29427,7 @@
           <t>BLAISE Thibault</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>41589</t>
         </is>
@@ -29508,7 +29538,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -29566,7 +29596,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -29624,7 +29654,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -29682,7 +29712,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -29793,7 +29823,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -29851,7 +29881,7 @@
           <t>DOMENJO Jordi</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35739</t>
         </is>
@@ -29909,7 +29939,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -29967,7 +29997,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -30025,7 +30055,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -30083,7 +30113,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -30141,7 +30171,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -30199,7 +30229,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -30257,7 +30287,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -30368,7 +30398,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -30426,7 +30456,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -30484,7 +30514,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -30648,7 +30678,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -30706,7 +30736,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -30764,7 +30794,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -30822,7 +30852,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -30880,7 +30910,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -30938,7 +30968,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -31049,7 +31079,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -31107,7 +31137,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -31218,7 +31248,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -31276,7 +31306,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -31334,7 +31364,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -31445,7 +31475,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -31503,7 +31533,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -31561,7 +31591,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -31619,7 +31649,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -31730,7 +31760,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -31788,7 +31818,7 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -31899,7 +31929,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -32010,7 +32040,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -32068,7 +32098,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -32126,7 +32156,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -32184,7 +32214,7 @@
           <t>DAMIENS Bastien</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>35584</t>
         </is>
@@ -32242,7 +32272,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -32300,7 +32330,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -32358,7 +32388,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -32416,7 +32446,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -32474,7 +32504,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -32532,7 +32562,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -32590,7 +32620,7 @@
           <t>KURT Michael</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
@@ -32648,7 +32678,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -32706,7 +32736,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -32764,7 +32794,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -32822,7 +32852,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -32880,7 +32910,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -32938,7 +32968,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -32996,7 +33026,7 @@
           <t>ROMEO Andrea</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>35502</t>
         </is>
@@ -33054,7 +33084,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -33112,7 +33142,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -33170,7 +33200,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -33228,7 +33258,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -33286,7 +33316,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -33344,7 +33374,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -33402,7 +33432,7 @@
           <t>MOLMENTI Daniele</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
@@ -33460,7 +33490,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -33518,7 +33548,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -33576,7 +33606,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -33634,7 +33664,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -33692,7 +33722,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -33760,7 +33790,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -33828,7 +33858,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -33896,7 +33926,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -33964,7 +33994,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -34032,7 +34062,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -34100,7 +34130,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -34168,7 +34198,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -34236,7 +34266,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -34304,7 +34334,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -34372,7 +34402,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -34440,7 +34470,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -34508,7 +34538,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -34576,7 +34606,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -34697,7 +34727,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -34891,7 +34921,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -34959,7 +34989,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -35090,7 +35120,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -35158,7 +35188,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -35226,7 +35256,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -35294,7 +35324,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -35362,7 +35392,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -35430,7 +35460,7 @@
           <t>KURT Michael</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
@@ -35498,7 +35528,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -35566,7 +35596,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -35634,7 +35664,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -35702,7 +35732,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -35909,7 +35939,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -35967,7 +35997,7 @@
           <t>LI Lu</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>37086</t>
         </is>
@@ -36025,7 +36055,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -36083,7 +36113,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -36141,7 +36171,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -36199,7 +36229,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -36257,7 +36287,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -36315,7 +36345,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -36373,7 +36403,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -36431,7 +36461,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -36542,7 +36572,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -36600,7 +36630,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U617" t="inlineStr">
+      <c r="X617" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -36658,7 +36688,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -36716,7 +36746,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U619" t="inlineStr">
+      <c r="X619" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -36774,7 +36804,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -36832,7 +36862,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -36890,7 +36920,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -36948,7 +36978,7 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -37006,7 +37036,7 @@
           <t>ORNSTOVA Eva</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>35052</t>
         </is>
@@ -37064,7 +37094,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -37122,7 +37152,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -37180,7 +37210,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -37238,7 +37268,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -37296,7 +37326,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -37407,7 +37437,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -37465,7 +37495,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -37576,7 +37606,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -37639,12 +37669,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V635" t="inlineStr">
+      <c r="Y635" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -37707,12 +37737,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V636" t="inlineStr">
+      <c r="Y636" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -37775,12 +37805,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V637" t="inlineStr">
+      <c r="Y637" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -37843,12 +37873,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V638" t="inlineStr">
+      <c r="Y638" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -37911,12 +37941,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V639" t="inlineStr">
+      <c r="Y639" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -37979,7 +38009,7 @@
           <t>FRANKLIN Zachary</t>
         </is>
       </c>
-      <c r="U640" t="inlineStr">
+      <c r="X640" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -38042,12 +38072,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V641" t="inlineStr">
+      <c r="Y641" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -38168,12 +38198,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V643" t="inlineStr">
+      <c r="Y643" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -38236,12 +38266,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V644" t="inlineStr">
+      <c r="Y644" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -38304,12 +38334,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U645" t="inlineStr">
+      <c r="X645" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V645" t="inlineStr">
+      <c r="Y645" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -38372,12 +38402,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V646" t="inlineStr">
+      <c r="Y646" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -38440,12 +38470,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V647" t="inlineStr">
+      <c r="Y647" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -38508,12 +38538,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V648" t="inlineStr">
+      <c r="Y648" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -38576,12 +38606,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V649" t="inlineStr">
+      <c r="Y649" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -38644,12 +38674,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U650" t="inlineStr">
+      <c r="X650" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V650" t="inlineStr">
+      <c r="Y650" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -38712,12 +38742,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U651" t="inlineStr">
+      <c r="X651" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V651" t="inlineStr">
+      <c r="Y651" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -38780,12 +38810,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U652" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V652" t="inlineStr">
+      <c r="Y652" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -38848,12 +38878,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U653" t="inlineStr">
+      <c r="X653" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V653" t="inlineStr">
+      <c r="Y653" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -38916,12 +38946,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U654" t="inlineStr">
+      <c r="X654" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V654" t="inlineStr">
+      <c r="Y654" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -38989,7 +39019,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U655" t="inlineStr">
+      <c r="X655" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -39057,7 +39087,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U656" t="inlineStr">
+      <c r="X656" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -39125,7 +39155,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U657" t="inlineStr">
+      <c r="X657" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -39193,7 +39223,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U658" t="inlineStr">
+      <c r="X658" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -39261,7 +39291,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U659" t="inlineStr">
+      <c r="X659" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -39329,7 +39359,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U660" t="inlineStr">
+      <c r="X660" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -39397,7 +39427,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U661" t="inlineStr">
+      <c r="X661" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -39465,7 +39495,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U662" t="inlineStr">
+      <c r="X662" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -39533,7 +39563,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U663" t="inlineStr">
+      <c r="X663" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -39601,7 +39631,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U664" t="inlineStr">
+      <c r="X664" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -39674,12 +39704,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U665" t="inlineStr">
+      <c r="X665" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V665" t="inlineStr">
+      <c r="Y665" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -39752,7 +39782,7 @@
           <t>FRANKLIN Zachary</t>
         </is>
       </c>
-      <c r="U666" t="inlineStr">
+      <c r="X666" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -39825,12 +39855,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U667" t="inlineStr">
+      <c r="X667" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V667" t="inlineStr">
+      <c r="Y667" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -39903,12 +39933,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U668" t="inlineStr">
+      <c r="X668" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V668" t="inlineStr">
+      <c r="Y668" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -39981,12 +40011,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U669" t="inlineStr">
+      <c r="X669" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V669" t="inlineStr">
+      <c r="Y669" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -40059,12 +40089,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U670" t="inlineStr">
+      <c r="X670" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V670" t="inlineStr">
+      <c r="Y670" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -40137,12 +40167,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U671" t="inlineStr">
+      <c r="X671" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V671" t="inlineStr">
+      <c r="Y671" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -40215,12 +40245,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U672" t="inlineStr">
+      <c r="X672" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V672" t="inlineStr">
+      <c r="Y672" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -40293,12 +40323,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U673" t="inlineStr">
+      <c r="X673" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V673" t="inlineStr">
+      <c r="Y673" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -40371,12 +40401,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U674" t="inlineStr">
+      <c r="X674" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V674" t="inlineStr">
+      <c r="Y674" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
